--- a/06_sources/ESS/ESS_RDC_tous_regimes/ESS RDC tous régimes.xlsx
+++ b/06_sources/ESS/ESS_RDC_tous_regimes/ESS RDC tous régimes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\irra\Documents\Computadora OIT\Carpeta documentos\DWT_CO_Yaoundé\RDC\Bulletin statisque\Deuxieme edition bulleting statistic\livrables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a72b42ab654a8fcc/Bureau/RDC Bulletin V1/Bulletin_rdc_2026_agents/06_sources/ESS/ESS_RDC_tous_regimes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F945B42-2BB2-48F2-8CA3-EAF0C4393F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{2F945B42-2BB2-48F2-8CA3-EAF0C4393F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEFEB40A-11D1-4D36-B0EF-2D994A7D6FEC}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Schemes Inventory" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,20 @@
     <sheet name="Scheme 14" sheetId="15" r:id="rId15"/>
     <sheet name="Scheme 15" sheetId="16" r:id="rId16"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -858,7 +871,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -915,6 +928,12 @@
         <fgColor rgb="FFF0F0F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -928,7 +947,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -959,10 +978,11 @@
     <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -974,10 +994,11 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1283,100 +1304,2361 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AR18"/>
-  <sheetFormatPr defaultColWidth="14.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="14.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.90625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="23.08984375" style="10" customWidth="1"/>
-    <col min="4" max="4" width="21.90625" style="10" customWidth="1"/>
-    <col min="5" max="5" width="20.08984375" style="10" customWidth="1"/>
-    <col min="6" max="6" width="20.1796875" style="10" customWidth="1"/>
-    <col min="7" max="7" width="18.1796875" style="10" customWidth="1"/>
-    <col min="8" max="8" width="21.81640625" style="10" customWidth="1"/>
-    <col min="9" max="9" width="19.08984375" style="10" customWidth="1"/>
-    <col min="10" max="10" width="17.6328125" style="10" customWidth="1"/>
-    <col min="11" max="11" width="19.81640625" style="10" customWidth="1"/>
-    <col min="12" max="12" width="17.453125" style="10" customWidth="1"/>
-    <col min="13" max="13" width="20.08984375" style="10" customWidth="1"/>
-    <col min="14" max="14" width="8.453125" style="10" customWidth="1"/>
-    <col min="15" max="15" width="12.90625" style="10" customWidth="1"/>
-    <col min="16" max="16" width="15.1796875" style="10" customWidth="1"/>
-    <col min="17" max="17" width="12.1796875" style="10" customWidth="1"/>
-    <col min="19" max="19" width="12.08984375" style="10" customWidth="1"/>
-    <col min="20" max="20" width="13.36328125" style="10" customWidth="1"/>
-    <col min="21" max="21" width="13.81640625" style="10" customWidth="1"/>
-    <col min="22" max="22" width="12.81640625" style="10" customWidth="1"/>
-    <col min="24" max="24" width="20.08984375" style="10" customWidth="1"/>
-    <col min="25" max="25" width="8.453125" style="10" customWidth="1"/>
-    <col min="26" max="26" width="11.6328125" style="10" customWidth="1"/>
-    <col min="27" max="27" width="14.90625" style="10" customWidth="1"/>
-    <col min="28" max="28" width="12.453125" style="10" customWidth="1"/>
-    <col min="29" max="29" width="15.453125" style="10" customWidth="1"/>
-    <col min="31" max="31" width="12.1796875" style="10" customWidth="1"/>
-    <col min="32" max="32" width="15.6328125" style="10" customWidth="1"/>
-    <col min="33" max="33" width="16.453125" style="10" customWidth="1"/>
-    <col min="34" max="34" width="16.1796875" style="10" customWidth="1"/>
-    <col min="35" max="35" width="20.08984375" style="10" customWidth="1"/>
-    <col min="36" max="36" width="8.453125" style="10" customWidth="1"/>
-    <col min="37" max="37" width="17.81640625" style="10" customWidth="1"/>
-    <col min="39" max="39" width="15.6328125" style="10" customWidth="1"/>
-    <col min="40" max="40" width="20.08984375" style="10" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" style="10" customWidth="1"/>
+    <col min="3" max="3" width="23.109375" style="10" customWidth="1"/>
+    <col min="4" max="4" width="21.88671875" style="10" customWidth="1"/>
+    <col min="5" max="5" width="20.109375" style="10" customWidth="1"/>
+    <col min="6" max="6" width="20.21875" style="10" customWidth="1"/>
+    <col min="7" max="7" width="18.21875" style="10" customWidth="1"/>
+    <col min="8" max="8" width="21.77734375" style="10" customWidth="1"/>
+    <col min="9" max="9" width="19.109375" style="10" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" style="10" customWidth="1"/>
+    <col min="11" max="11" width="19.77734375" style="10" customWidth="1"/>
+    <col min="12" max="12" width="17.44140625" style="10" customWidth="1"/>
+    <col min="13" max="13" width="20.109375" style="10" customWidth="1"/>
+    <col min="14" max="14" width="8.44140625" style="10" customWidth="1"/>
+    <col min="15" max="15" width="12.88671875" style="10" customWidth="1"/>
+    <col min="16" max="16" width="15.21875" style="10" customWidth="1"/>
+    <col min="17" max="17" width="12.21875" style="10" customWidth="1"/>
+    <col min="19" max="19" width="12.109375" style="10" customWidth="1"/>
+    <col min="20" max="20" width="13.33203125" style="10" customWidth="1"/>
+    <col min="21" max="21" width="13.77734375" style="10" customWidth="1"/>
+    <col min="22" max="22" width="12.77734375" style="10" customWidth="1"/>
+    <col min="24" max="24" width="20.109375" style="10" customWidth="1"/>
+    <col min="25" max="25" width="8.44140625" style="10" customWidth="1"/>
+    <col min="26" max="26" width="11.6640625" style="10" customWidth="1"/>
+    <col min="27" max="27" width="14.88671875" style="10" customWidth="1"/>
+    <col min="28" max="28" width="12.44140625" style="10" customWidth="1"/>
+    <col min="29" max="29" width="15.44140625" style="10" customWidth="1"/>
+    <col min="31" max="31" width="12.21875" style="10" customWidth="1"/>
+    <col min="32" max="32" width="15.6640625" style="10" customWidth="1"/>
+    <col min="33" max="33" width="16.44140625" style="10" customWidth="1"/>
+    <col min="34" max="34" width="16.21875" style="10" customWidth="1"/>
+    <col min="35" max="35" width="20.109375" style="10" customWidth="1"/>
+    <col min="36" max="36" width="8.44140625" style="10" customWidth="1"/>
+    <col min="37" max="37" width="17.77734375" style="10" customWidth="1"/>
+    <col min="39" max="39" width="15.6640625" style="10" customWidth="1"/>
+    <col min="40" max="40" width="20.109375" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:44" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16"/>
+      <c r="AA1" s="16"/>
+      <c r="AB1" s="16"/>
+      <c r="AC1" s="16"/>
+      <c r="AD1" s="16"/>
+      <c r="AE1" s="16"/>
+      <c r="AF1" s="16"/>
+      <c r="AG1" s="16"/>
+      <c r="AH1" s="16"/>
+      <c r="AI1" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ1" s="16"/>
+      <c r="AK1" s="16"/>
+      <c r="AL1" s="16"/>
+      <c r="AM1" s="16"/>
+      <c r="AN1" s="16"/>
+      <c r="AO1" s="16"/>
+      <c r="AP1" s="16"/>
+      <c r="AQ1" s="16"/>
+      <c r="AR1" s="2"/>
+    </row>
+    <row r="2" spans="1:44" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="S2" s="16"/>
+      <c r="T2" s="16"/>
+      <c r="U2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="V2" s="16"/>
+      <c r="W2" s="16"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+      <c r="AC2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD2" s="16"/>
+      <c r="AE2" s="16"/>
+      <c r="AF2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG2" s="16"/>
+      <c r="AH2" s="16"/>
+      <c r="AI2" s="3"/>
+      <c r="AJ2" s="3"/>
+      <c r="AK2" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL2" s="16"/>
+      <c r="AM2" s="16"/>
+      <c r="AN2" s="16"/>
+      <c r="AO2" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP2" s="16"/>
+      <c r="AQ2" s="16"/>
+      <c r="AR2" s="4"/>
+    </row>
+    <row r="3" spans="1:44" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="T3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="V3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="W3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="X3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AL3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="AO3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP3" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AQ3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR3" s="8"/>
+    </row>
+    <row r="4" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="O4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="U4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="V4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="W4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="X4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ4" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="R5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="S5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="U5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="V5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="W5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="X5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ5" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="P6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="R6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="S6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="U6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="V6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="W6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="X6" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y6" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z6" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI6" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ6" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AK6" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="AL6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO6" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="AP6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ6" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="R7" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="U7" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="V7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="W7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="X7" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y7" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z7" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC7" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF7" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI7" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ7" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AK7" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN7" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="AO7" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ7" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="P8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="R8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="S8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="U8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="V8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="W8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="X8" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y8" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z8" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ8" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:44" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="J9" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="O9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="P9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="R9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="S9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="T9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="U9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="V9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="W9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="X9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ9" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:44" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="I10" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="J10" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="M10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="O10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="P10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="R10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="S10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="T10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="U10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="V10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="W10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="X10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ10" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:44" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="J11" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="M11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="O11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="P11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="R11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="S11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="T11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="U11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="V11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="W11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="X11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ11" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:44" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="M12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="O12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="P12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="R12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="S12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="T12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="U12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="V12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="W12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="X12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ12" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:44" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="J13" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="K13" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="L13" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="M13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="O13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="P13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="R13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="S13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="T13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="U13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="V13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="W13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="X13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ13" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="P14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="R14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="S14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="U14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="V14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="W14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="X14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ14" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="P15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="R15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="S15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="U15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="V15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="W15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="X15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ15" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="P16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="R16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="S16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="U16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="V16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="W16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="X16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ16" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="P17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="R17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="S17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="U17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="V17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="W17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="X17" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y17" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z17" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI17" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AJ17" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AK17" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="AL17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO17" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="AP17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ17" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="O18" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="P18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="R18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="S18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="U18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="V18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="W18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="X18" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y18" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z18" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI18" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ18" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AK18" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="AL18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO18" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="AP18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ18" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:L2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="M1:W1"/>
+    <mergeCell ref="AO2:AQ2"/>
+    <mergeCell ref="AI1:AQ1"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AC2:AE2"/>
+    <mergeCell ref="AF2:AH2"/>
+    <mergeCell ref="X1:AH1"/>
+    <mergeCell ref="AK2:AN2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:AU4"/>
+  <sheetFormatPr defaultColWidth="14.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="14.21875" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>122</v>
+      </c>
       <c r="F1" s="13"/>
       <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
+      <c r="H1" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>124</v>
+      </c>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
       <c r="L1" s="13"/>
-      <c r="M1" s="12" t="s">
-        <v>1</v>
-      </c>
+      <c r="M1" s="13"/>
       <c r="N1" s="13"/>
       <c r="O1" s="13"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15"/>
-      <c r="X1" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="15"/>
-      <c r="AA1" s="15"/>
-      <c r="AB1" s="15"/>
-      <c r="AC1" s="15"/>
-      <c r="AD1" s="15"/>
-      <c r="AE1" s="15"/>
-      <c r="AF1" s="15"/>
-      <c r="AG1" s="15"/>
-      <c r="AH1" s="15"/>
-      <c r="AI1" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ1" s="15"/>
-      <c r="AK1" s="15"/>
-      <c r="AL1" s="15"/>
-      <c r="AM1" s="15"/>
-      <c r="AN1" s="15"/>
-      <c r="AO1" s="15"/>
-      <c r="AP1" s="15"/>
-      <c r="AQ1" s="15"/>
-      <c r="AR1" s="2"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="AI1" s="13"/>
+      <c r="AJ1" s="13"/>
+      <c r="AK1" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="AL1" s="13"/>
+      <c r="AM1" s="13"/>
+      <c r="AN1" s="13"/>
+      <c r="AO1" s="13"/>
+      <c r="AP1" s="13"/>
+      <c r="AQ1" s="13"/>
+      <c r="AR1" s="13"/>
+      <c r="AS1" s="13"/>
+      <c r="AT1" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="AU1" s="9" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="2" spans="1:44" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="13"/>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -1385,2297 +3667,36 @@
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
+      <c r="I2" s="12" t="s">
+        <v>130</v>
+      </c>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="14" t="s">
+      <c r="L2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="14" t="s">
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="15"/>
-      <c r="AC2" s="14" t="s">
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="AD2" s="15"/>
-      <c r="AE2" s="15"/>
-      <c r="AF2" s="14" t="s">
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="AG2" s="15"/>
-      <c r="AH2" s="15"/>
-      <c r="AI2" s="3"/>
-      <c r="AJ2" s="3"/>
-      <c r="AK2" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL2" s="15"/>
-      <c r="AM2" s="15"/>
-      <c r="AN2" s="15"/>
-      <c r="AO2" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="AP2" s="15"/>
-      <c r="AQ2" s="15"/>
-      <c r="AR2" s="4"/>
-    </row>
-    <row r="3" spans="1:44" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="S3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="T3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="U3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="V3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="W3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="X3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="AA3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="AD3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="AE3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="AG3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="AI3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AJ3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="AK3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="AL3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="AN3" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="AO3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="AP3" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="AQ3" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="AR3" s="8"/>
-    </row>
-    <row r="4" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="O4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="P4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="R4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="S4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="V4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="X4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AN4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ4" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="P5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="R5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="S5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="V5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="X5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AN5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ5" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="M6" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="N6" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="O6" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="P6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="R6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="S6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="V6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="X6" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y6" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z6" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI6" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="AJ6" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="AK6" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="AL6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AN6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO6" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="AP6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ6" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="O7" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="P7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="R7" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="S7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U7" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="V7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="X7" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y7" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z7" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC7" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF7" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="AG7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI7" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ7" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="AK7" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="AL7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AN7" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="AO7" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="AP7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ7" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="P8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="R8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="S8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="V8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="X8" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y8" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z8" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AA8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AN8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ8" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="O9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="P9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="R9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="S9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="V9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="X9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AN9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ9" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="M10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="N10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="O10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="P10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="R10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="S10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="V10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="X10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AN10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ10" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="P11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="R11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="S11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="V11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="X11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AN11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ11" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="N12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="O12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="P12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="R12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="S12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="V12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="X12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AN12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ12" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="R13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="S13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="V13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="X13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AN13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ13" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="L14" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="M14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="N14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="O14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="P14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="R14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="S14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="V14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="X14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AN14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ14" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="N15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="O15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="P15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="R15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="S15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="V15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="X15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AN15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ15" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="M16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="N16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="O16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="P16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="R16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="S16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="V16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="X16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AN16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ16" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="M17" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="N17" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="O17" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="P17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="R17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="S17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="V17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="X17" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="Y17" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z17" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI17" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="AJ17" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="AK17" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="AL17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AN17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO17" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="AP17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ17" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="M18" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="N18" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="O18" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="P18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="R18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="S18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="V18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="X18" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y18" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z18" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI18" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="AJ18" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="AK18" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="AL18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AN18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO18" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="AP18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ18" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="AO2:AQ2"/>
-    <mergeCell ref="AI1:AQ1"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AC2:AE2"/>
-    <mergeCell ref="AF2:AH2"/>
-    <mergeCell ref="X1:AH1"/>
-    <mergeCell ref="AK2:AN2"/>
-    <mergeCell ref="A1:L2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="M1:W1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:AU4"/>
-  <sheetFormatPr defaultColWidth="14.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="16384" width="14.1796875" style="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17"/>
-      <c r="AK1" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17"/>
-      <c r="AQ1" s="17"/>
-      <c r="AR1" s="17"/>
-      <c r="AS1" s="17"/>
-      <c r="AT1" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="AU1" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-      <c r="U2" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y2" s="17"/>
-      <c r="Z2" s="17"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
       <c r="AA2" s="5" t="s">
         <v>131</v>
       </c>
@@ -3685,48 +3706,48 @@
       <c r="AC2" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="AD2" s="18" t="s">
+      <c r="AD2" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="AE2" s="17"/>
-      <c r="AF2" s="18" t="s">
+      <c r="AE2" s="13"/>
+      <c r="AF2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="AG2" s="17"/>
-      <c r="AH2" s="18" t="s">
+      <c r="AG2" s="13"/>
+      <c r="AH2" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="AI2" s="17"/>
-      <c r="AJ2" s="17"/>
-      <c r="AK2" s="18" t="s">
+      <c r="AI2" s="13"/>
+      <c r="AJ2" s="13"/>
+      <c r="AK2" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="AL2" s="17"/>
-      <c r="AM2" s="18" t="s">
+      <c r="AL2" s="13"/>
+      <c r="AM2" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="AN2" s="17"/>
+      <c r="AN2" s="13"/>
       <c r="AO2" s="5" t="s">
         <v>139</v>
       </c>
       <c r="AP2" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="AQ2" s="18" t="s">
+      <c r="AQ2" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="AR2" s="17"/>
+      <c r="AR2" s="13"/>
       <c r="AS2" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="AT2" s="17"/>
+      <c r="AT2" s="13"/>
       <c r="AU2" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
       <c r="C3" s="11" t="s">
         <v>143</v>
       </c>
@@ -3856,12 +3877,12 @@
       <c r="AS3" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="AT3" s="17"/>
+      <c r="AT3" s="13"/>
       <c r="AU3" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>210</v>
       </c>
@@ -3926,6 +3947,16 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:Q1"/>
+    <mergeCell ref="R1:Z1"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AT1:AT3"/>
     <mergeCell ref="AK1:AS1"/>
     <mergeCell ref="I2:K2"/>
@@ -3940,16 +3971,6 @@
     <mergeCell ref="AK2:AL2"/>
     <mergeCell ref="AM2:AN2"/>
     <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:Q1"/>
-    <mergeCell ref="R1:Z1"/>
-    <mergeCell ref="AA1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3958,125 +3979,125 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:AU4"/>
-  <sheetFormatPr defaultColWidth="14.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="14.1796875" style="10"/>
+    <col min="1" max="16384" width="14.21875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="18" t="s">
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="12" t="s">
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="12" t="s">
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="12" t="s">
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17"/>
-      <c r="AK1" s="12" t="s">
+      <c r="AI1" s="13"/>
+      <c r="AJ1" s="13"/>
+      <c r="AK1" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17"/>
-      <c r="AQ1" s="17"/>
-      <c r="AR1" s="17"/>
-      <c r="AS1" s="17"/>
-      <c r="AT1" s="18" t="s">
+      <c r="AL1" s="13"/>
+      <c r="AM1" s="13"/>
+      <c r="AN1" s="13"/>
+      <c r="AO1" s="13"/>
+      <c r="AP1" s="13"/>
+      <c r="AQ1" s="13"/>
+      <c r="AR1" s="13"/>
+      <c r="AS1" s="13"/>
+      <c r="AT1" s="12" t="s">
         <v>129</v>
       </c>
       <c r="AU1" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18" t="s">
+    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="18" t="s">
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="18" t="s">
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="18" t="s">
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-      <c r="U2" s="18" t="s">
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="18" t="s">
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="Y2" s="17"/>
-      <c r="Z2" s="17"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
       <c r="AA2" s="5" t="s">
         <v>131</v>
       </c>
@@ -4086,48 +4107,48 @@
       <c r="AC2" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="AD2" s="18" t="s">
+      <c r="AD2" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="AE2" s="17"/>
-      <c r="AF2" s="18" t="s">
+      <c r="AE2" s="13"/>
+      <c r="AF2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="AG2" s="17"/>
-      <c r="AH2" s="18" t="s">
+      <c r="AG2" s="13"/>
+      <c r="AH2" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="AI2" s="17"/>
-      <c r="AJ2" s="17"/>
-      <c r="AK2" s="18" t="s">
+      <c r="AI2" s="13"/>
+      <c r="AJ2" s="13"/>
+      <c r="AK2" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="AL2" s="17"/>
-      <c r="AM2" s="18" t="s">
+      <c r="AL2" s="13"/>
+      <c r="AM2" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="AN2" s="17"/>
+      <c r="AN2" s="13"/>
       <c r="AO2" s="5" t="s">
         <v>139</v>
       </c>
       <c r="AP2" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="AQ2" s="18" t="s">
+      <c r="AQ2" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="AR2" s="17"/>
+      <c r="AR2" s="13"/>
       <c r="AS2" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="AT2" s="17"/>
+      <c r="AT2" s="13"/>
       <c r="AU2" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
       <c r="C3" s="11" t="s">
         <v>143</v>
       </c>
@@ -4257,12 +4278,12 @@
       <c r="AS3" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="AT3" s="17"/>
+      <c r="AT3" s="13"/>
       <c r="AU3" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>212</v>
       </c>
@@ -4341,6 +4362,16 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:Q1"/>
+    <mergeCell ref="R1:Z1"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AT1:AT3"/>
     <mergeCell ref="AK1:AS1"/>
     <mergeCell ref="I2:K2"/>
@@ -4355,16 +4386,6 @@
     <mergeCell ref="AK2:AL2"/>
     <mergeCell ref="AM2:AN2"/>
     <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:Q1"/>
-    <mergeCell ref="R1:Z1"/>
-    <mergeCell ref="AA1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4373,125 +4394,125 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:AU4"/>
-  <sheetFormatPr defaultColWidth="14.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="14.1796875" style="10"/>
+    <col min="1" max="16384" width="14.21875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="18" t="s">
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="12" t="s">
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="12" t="s">
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="12" t="s">
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17"/>
-      <c r="AK1" s="12" t="s">
+      <c r="AI1" s="13"/>
+      <c r="AJ1" s="13"/>
+      <c r="AK1" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17"/>
-      <c r="AQ1" s="17"/>
-      <c r="AR1" s="17"/>
-      <c r="AS1" s="17"/>
-      <c r="AT1" s="18" t="s">
+      <c r="AL1" s="13"/>
+      <c r="AM1" s="13"/>
+      <c r="AN1" s="13"/>
+      <c r="AO1" s="13"/>
+      <c r="AP1" s="13"/>
+      <c r="AQ1" s="13"/>
+      <c r="AR1" s="13"/>
+      <c r="AS1" s="13"/>
+      <c r="AT1" s="12" t="s">
         <v>129</v>
       </c>
       <c r="AU1" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18" t="s">
+    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="18" t="s">
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="18" t="s">
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="18" t="s">
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-      <c r="U2" s="18" t="s">
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="18" t="s">
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="Y2" s="17"/>
-      <c r="Z2" s="17"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
       <c r="AA2" s="5" t="s">
         <v>131</v>
       </c>
@@ -4501,48 +4522,48 @@
       <c r="AC2" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="AD2" s="18" t="s">
+      <c r="AD2" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="AE2" s="17"/>
-      <c r="AF2" s="18" t="s">
+      <c r="AE2" s="13"/>
+      <c r="AF2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="AG2" s="17"/>
-      <c r="AH2" s="18" t="s">
+      <c r="AG2" s="13"/>
+      <c r="AH2" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="AI2" s="17"/>
-      <c r="AJ2" s="17"/>
-      <c r="AK2" s="18" t="s">
+      <c r="AI2" s="13"/>
+      <c r="AJ2" s="13"/>
+      <c r="AK2" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="AL2" s="17"/>
-      <c r="AM2" s="18" t="s">
+      <c r="AL2" s="13"/>
+      <c r="AM2" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="AN2" s="17"/>
+      <c r="AN2" s="13"/>
       <c r="AO2" s="5" t="s">
         <v>139</v>
       </c>
       <c r="AP2" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="AQ2" s="18" t="s">
+      <c r="AQ2" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="AR2" s="17"/>
+      <c r="AR2" s="13"/>
       <c r="AS2" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="AT2" s="17"/>
+      <c r="AT2" s="13"/>
       <c r="AU2" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
       <c r="C3" s="11" t="s">
         <v>143</v>
       </c>
@@ -4672,12 +4693,12 @@
       <c r="AS3" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="AT3" s="17"/>
+      <c r="AT3" s="13"/>
       <c r="AU3" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>214</v>
       </c>
@@ -4738,6 +4759,16 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:Q1"/>
+    <mergeCell ref="R1:Z1"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AT1:AT3"/>
     <mergeCell ref="AK1:AS1"/>
     <mergeCell ref="I2:K2"/>
@@ -4752,16 +4783,6 @@
     <mergeCell ref="AK2:AL2"/>
     <mergeCell ref="AM2:AN2"/>
     <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:Q1"/>
-    <mergeCell ref="R1:Z1"/>
-    <mergeCell ref="AA1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4770,125 +4791,125 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:AU3"/>
-  <sheetFormatPr defaultColWidth="14.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="14.1796875" style="10"/>
+    <col min="1" max="16384" width="14.21875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="18" t="s">
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="12" t="s">
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="12" t="s">
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="12" t="s">
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17"/>
-      <c r="AK1" s="12" t="s">
+      <c r="AI1" s="13"/>
+      <c r="AJ1" s="13"/>
+      <c r="AK1" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17"/>
-      <c r="AQ1" s="17"/>
-      <c r="AR1" s="17"/>
-      <c r="AS1" s="17"/>
-      <c r="AT1" s="18" t="s">
+      <c r="AL1" s="13"/>
+      <c r="AM1" s="13"/>
+      <c r="AN1" s="13"/>
+      <c r="AO1" s="13"/>
+      <c r="AP1" s="13"/>
+      <c r="AQ1" s="13"/>
+      <c r="AR1" s="13"/>
+      <c r="AS1" s="13"/>
+      <c r="AT1" s="12" t="s">
         <v>129</v>
       </c>
       <c r="AU1" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18" t="s">
+    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="18" t="s">
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="18" t="s">
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="18" t="s">
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-      <c r="U2" s="18" t="s">
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="18" t="s">
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="Y2" s="17"/>
-      <c r="Z2" s="17"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
       <c r="AA2" s="5" t="s">
         <v>131</v>
       </c>
@@ -4898,48 +4919,48 @@
       <c r="AC2" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="AD2" s="18" t="s">
+      <c r="AD2" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="AE2" s="17"/>
-      <c r="AF2" s="18" t="s">
+      <c r="AE2" s="13"/>
+      <c r="AF2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="AG2" s="17"/>
-      <c r="AH2" s="18" t="s">
+      <c r="AG2" s="13"/>
+      <c r="AH2" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="AI2" s="17"/>
-      <c r="AJ2" s="17"/>
-      <c r="AK2" s="18" t="s">
+      <c r="AI2" s="13"/>
+      <c r="AJ2" s="13"/>
+      <c r="AK2" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="AL2" s="17"/>
-      <c r="AM2" s="18" t="s">
+      <c r="AL2" s="13"/>
+      <c r="AM2" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="AN2" s="17"/>
+      <c r="AN2" s="13"/>
       <c r="AO2" s="5" t="s">
         <v>139</v>
       </c>
       <c r="AP2" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="AQ2" s="18" t="s">
+      <c r="AQ2" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="AR2" s="17"/>
+      <c r="AR2" s="13"/>
       <c r="AS2" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="AT2" s="17"/>
+      <c r="AT2" s="13"/>
       <c r="AU2" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
       <c r="C3" s="11" t="s">
         <v>143</v>
       </c>
@@ -5069,13 +5090,23 @@
       <c r="AS3" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="AT3" s="17"/>
+      <c r="AT3" s="13"/>
       <c r="AU3" s="9" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:Q1"/>
+    <mergeCell ref="R1:Z1"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AT1:AT3"/>
     <mergeCell ref="AK1:AS1"/>
     <mergeCell ref="I2:K2"/>
@@ -5090,16 +5121,6 @@
     <mergeCell ref="AK2:AL2"/>
     <mergeCell ref="AM2:AN2"/>
     <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:Q1"/>
-    <mergeCell ref="R1:Z1"/>
-    <mergeCell ref="AA1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5108,125 +5129,125 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:AU3"/>
-  <sheetFormatPr defaultColWidth="14.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="14.1796875" style="10"/>
+    <col min="1" max="16384" width="14.21875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="18" t="s">
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="12" t="s">
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="12" t="s">
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="12" t="s">
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17"/>
-      <c r="AK1" s="12" t="s">
+      <c r="AI1" s="13"/>
+      <c r="AJ1" s="13"/>
+      <c r="AK1" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17"/>
-      <c r="AQ1" s="17"/>
-      <c r="AR1" s="17"/>
-      <c r="AS1" s="17"/>
-      <c r="AT1" s="18" t="s">
+      <c r="AL1" s="13"/>
+      <c r="AM1" s="13"/>
+      <c r="AN1" s="13"/>
+      <c r="AO1" s="13"/>
+      <c r="AP1" s="13"/>
+      <c r="AQ1" s="13"/>
+      <c r="AR1" s="13"/>
+      <c r="AS1" s="13"/>
+      <c r="AT1" s="12" t="s">
         <v>129</v>
       </c>
       <c r="AU1" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18" t="s">
+    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="18" t="s">
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="18" t="s">
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="18" t="s">
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-      <c r="U2" s="18" t="s">
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="18" t="s">
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="Y2" s="17"/>
-      <c r="Z2" s="17"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
       <c r="AA2" s="5" t="s">
         <v>131</v>
       </c>
@@ -5236,48 +5257,48 @@
       <c r="AC2" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="AD2" s="18" t="s">
+      <c r="AD2" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="AE2" s="17"/>
-      <c r="AF2" s="18" t="s">
+      <c r="AE2" s="13"/>
+      <c r="AF2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="AG2" s="17"/>
-      <c r="AH2" s="18" t="s">
+      <c r="AG2" s="13"/>
+      <c r="AH2" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="AI2" s="17"/>
-      <c r="AJ2" s="17"/>
-      <c r="AK2" s="18" t="s">
+      <c r="AI2" s="13"/>
+      <c r="AJ2" s="13"/>
+      <c r="AK2" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="AL2" s="17"/>
-      <c r="AM2" s="18" t="s">
+      <c r="AL2" s="13"/>
+      <c r="AM2" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="AN2" s="17"/>
+      <c r="AN2" s="13"/>
       <c r="AO2" s="5" t="s">
         <v>139</v>
       </c>
       <c r="AP2" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="AQ2" s="18" t="s">
+      <c r="AQ2" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="AR2" s="17"/>
+      <c r="AR2" s="13"/>
       <c r="AS2" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="AT2" s="17"/>
+      <c r="AT2" s="13"/>
       <c r="AU2" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
       <c r="C3" s="11" t="s">
         <v>143</v>
       </c>
@@ -5407,13 +5428,23 @@
       <c r="AS3" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="AT3" s="17"/>
+      <c r="AT3" s="13"/>
       <c r="AU3" s="9" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:Q1"/>
+    <mergeCell ref="R1:Z1"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AT1:AT3"/>
     <mergeCell ref="AK1:AS1"/>
     <mergeCell ref="I2:K2"/>
@@ -5428,16 +5459,6 @@
     <mergeCell ref="AK2:AL2"/>
     <mergeCell ref="AM2:AN2"/>
     <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:Q1"/>
-    <mergeCell ref="R1:Z1"/>
-    <mergeCell ref="AA1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5446,125 +5467,125 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:AU7"/>
-  <sheetFormatPr defaultColWidth="14.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="14.1796875" style="10"/>
+    <col min="1" max="16384" width="14.21875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="18" t="s">
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="12" t="s">
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="12" t="s">
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="12" t="s">
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17"/>
-      <c r="AK1" s="12" t="s">
+      <c r="AI1" s="13"/>
+      <c r="AJ1" s="13"/>
+      <c r="AK1" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17"/>
-      <c r="AQ1" s="17"/>
-      <c r="AR1" s="17"/>
-      <c r="AS1" s="17"/>
-      <c r="AT1" s="18" t="s">
+      <c r="AL1" s="13"/>
+      <c r="AM1" s="13"/>
+      <c r="AN1" s="13"/>
+      <c r="AO1" s="13"/>
+      <c r="AP1" s="13"/>
+      <c r="AQ1" s="13"/>
+      <c r="AR1" s="13"/>
+      <c r="AS1" s="13"/>
+      <c r="AT1" s="12" t="s">
         <v>129</v>
       </c>
       <c r="AU1" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18" t="s">
+    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="18" t="s">
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="18" t="s">
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="18" t="s">
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-      <c r="U2" s="18" t="s">
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="18" t="s">
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="Y2" s="17"/>
-      <c r="Z2" s="17"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
       <c r="AA2" s="5" t="s">
         <v>131</v>
       </c>
@@ -5574,48 +5595,48 @@
       <c r="AC2" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="AD2" s="18" t="s">
+      <c r="AD2" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="AE2" s="17"/>
-      <c r="AF2" s="18" t="s">
+      <c r="AE2" s="13"/>
+      <c r="AF2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="AG2" s="17"/>
-      <c r="AH2" s="18" t="s">
+      <c r="AG2" s="13"/>
+      <c r="AH2" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="AI2" s="17"/>
-      <c r="AJ2" s="17"/>
-      <c r="AK2" s="18" t="s">
+      <c r="AI2" s="13"/>
+      <c r="AJ2" s="13"/>
+      <c r="AK2" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="AL2" s="17"/>
-      <c r="AM2" s="18" t="s">
+      <c r="AL2" s="13"/>
+      <c r="AM2" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="AN2" s="17"/>
+      <c r="AN2" s="13"/>
       <c r="AO2" s="5" t="s">
         <v>139</v>
       </c>
       <c r="AP2" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="AQ2" s="18" t="s">
+      <c r="AQ2" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="AR2" s="17"/>
+      <c r="AR2" s="13"/>
       <c r="AS2" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="AT2" s="17"/>
+      <c r="AT2" s="13"/>
       <c r="AU2" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
       <c r="C3" s="11" t="s">
         <v>143</v>
       </c>
@@ -5745,12 +5766,12 @@
       <c r="AS3" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="AT3" s="17"/>
+      <c r="AT3" s="13"/>
       <c r="AU3" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>216</v>
       </c>
@@ -5839,7 +5860,7 @@
       </c>
       <c r="AS4" s="9"/>
     </row>
-    <row r="5" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>220</v>
       </c>
@@ -5928,7 +5949,7 @@
       </c>
       <c r="AS5" s="9"/>
     </row>
-    <row r="6" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
         <v>221</v>
       </c>
@@ -6017,7 +6038,7 @@
       </c>
       <c r="AS6" s="9"/>
     </row>
-    <row r="7" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
         <v>224</v>
       </c>
@@ -6108,6 +6129,16 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:Q1"/>
+    <mergeCell ref="R1:Z1"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AT1:AT3"/>
     <mergeCell ref="AK1:AS1"/>
     <mergeCell ref="I2:K2"/>
@@ -6122,16 +6153,6 @@
     <mergeCell ref="AK2:AL2"/>
     <mergeCell ref="AM2:AN2"/>
     <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:Q1"/>
-    <mergeCell ref="R1:Z1"/>
-    <mergeCell ref="AA1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6140,125 +6161,125 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:AU14"/>
-  <sheetFormatPr defaultColWidth="14.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="14.1796875" style="10"/>
+    <col min="1" max="16384" width="14.21875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="18" t="s">
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="12" t="s">
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="12" t="s">
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="12" t="s">
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17"/>
-      <c r="AK1" s="12" t="s">
+      <c r="AI1" s="13"/>
+      <c r="AJ1" s="13"/>
+      <c r="AK1" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17"/>
-      <c r="AQ1" s="17"/>
-      <c r="AR1" s="17"/>
-      <c r="AS1" s="17"/>
-      <c r="AT1" s="18" t="s">
+      <c r="AL1" s="13"/>
+      <c r="AM1" s="13"/>
+      <c r="AN1" s="13"/>
+      <c r="AO1" s="13"/>
+      <c r="AP1" s="13"/>
+      <c r="AQ1" s="13"/>
+      <c r="AR1" s="13"/>
+      <c r="AS1" s="13"/>
+      <c r="AT1" s="12" t="s">
         <v>129</v>
       </c>
       <c r="AU1" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18" t="s">
+    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="18" t="s">
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="18" t="s">
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="18" t="s">
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-      <c r="U2" s="18" t="s">
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="18" t="s">
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="Y2" s="17"/>
-      <c r="Z2" s="17"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
       <c r="AA2" s="5" t="s">
         <v>131</v>
       </c>
@@ -6268,48 +6289,48 @@
       <c r="AC2" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="AD2" s="18" t="s">
+      <c r="AD2" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="AE2" s="17"/>
-      <c r="AF2" s="18" t="s">
+      <c r="AE2" s="13"/>
+      <c r="AF2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="AG2" s="17"/>
-      <c r="AH2" s="18" t="s">
+      <c r="AG2" s="13"/>
+      <c r="AH2" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="AI2" s="17"/>
-      <c r="AJ2" s="17"/>
-      <c r="AK2" s="18" t="s">
+      <c r="AI2" s="13"/>
+      <c r="AJ2" s="13"/>
+      <c r="AK2" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="AL2" s="17"/>
-      <c r="AM2" s="18" t="s">
+      <c r="AL2" s="13"/>
+      <c r="AM2" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="AN2" s="17"/>
+      <c r="AN2" s="13"/>
       <c r="AO2" s="5" t="s">
         <v>139</v>
       </c>
       <c r="AP2" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="AQ2" s="18" t="s">
+      <c r="AQ2" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="AR2" s="17"/>
+      <c r="AR2" s="13"/>
       <c r="AS2" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="AT2" s="17"/>
+      <c r="AT2" s="13"/>
       <c r="AU2" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
       <c r="C3" s="11" t="s">
         <v>143</v>
       </c>
@@ -6439,12 +6460,12 @@
       <c r="AS3" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="AT3" s="17"/>
+      <c r="AT3" s="13"/>
       <c r="AU3" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>226</v>
       </c>
@@ -6533,7 +6554,7 @@
       </c>
       <c r="AS4" s="9"/>
     </row>
-    <row r="5" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>228</v>
       </c>
@@ -6622,7 +6643,7 @@
       </c>
       <c r="AS5" s="9"/>
     </row>
-    <row r="6" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
         <v>229</v>
       </c>
@@ -6711,7 +6732,7 @@
       </c>
       <c r="AS6" s="9"/>
     </row>
-    <row r="7" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
         <v>230</v>
       </c>
@@ -6800,7 +6821,7 @@
       </c>
       <c r="AS7" s="9"/>
     </row>
-    <row r="8" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
         <v>231</v>
       </c>
@@ -6889,7 +6910,7 @@
       </c>
       <c r="AS8" s="9"/>
     </row>
-    <row r="9" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>232</v>
       </c>
@@ -6976,7 +6997,7 @@
       </c>
       <c r="AS9" s="9"/>
     </row>
-    <row r="10" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
         <v>234</v>
       </c>
@@ -7063,7 +7084,7 @@
       </c>
       <c r="AS10" s="9"/>
     </row>
-    <row r="11" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
         <v>235</v>
       </c>
@@ -7150,7 +7171,7 @@
       </c>
       <c r="AS11" s="9"/>
     </row>
-    <row r="12" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
         <v>236</v>
       </c>
@@ -7237,7 +7258,7 @@
       </c>
       <c r="AS12" s="9"/>
     </row>
-    <row r="13" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
         <v>237</v>
       </c>
@@ -7324,7 +7345,7 @@
       </c>
       <c r="AS13" s="9"/>
     </row>
-    <row r="14" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
         <v>238</v>
       </c>
@@ -7413,6 +7434,16 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:Q1"/>
+    <mergeCell ref="R1:Z1"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AT1:AT3"/>
     <mergeCell ref="AK1:AS1"/>
     <mergeCell ref="I2:K2"/>
@@ -7427,16 +7458,6 @@
     <mergeCell ref="AK2:AL2"/>
     <mergeCell ref="AM2:AN2"/>
     <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:Q1"/>
-    <mergeCell ref="R1:Z1"/>
-    <mergeCell ref="AA1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7445,125 +7466,125 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AU5"/>
-  <sheetFormatPr defaultColWidth="14.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="14.1796875" style="10"/>
+    <col min="1" max="16384" width="14.21875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="18" t="s">
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="12" t="s">
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="12" t="s">
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="12" t="s">
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17"/>
-      <c r="AK1" s="12" t="s">
+      <c r="AI1" s="13"/>
+      <c r="AJ1" s="13"/>
+      <c r="AK1" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17"/>
-      <c r="AQ1" s="17"/>
-      <c r="AR1" s="17"/>
-      <c r="AS1" s="17"/>
-      <c r="AT1" s="18" t="s">
+      <c r="AL1" s="13"/>
+      <c r="AM1" s="13"/>
+      <c r="AN1" s="13"/>
+      <c r="AO1" s="13"/>
+      <c r="AP1" s="13"/>
+      <c r="AQ1" s="13"/>
+      <c r="AR1" s="13"/>
+      <c r="AS1" s="13"/>
+      <c r="AT1" s="12" t="s">
         <v>129</v>
       </c>
       <c r="AU1" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18" t="s">
+    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="18" t="s">
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="18" t="s">
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="18" t="s">
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-      <c r="U2" s="18" t="s">
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="18" t="s">
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="Y2" s="17"/>
-      <c r="Z2" s="17"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
       <c r="AA2" s="5" t="s">
         <v>131</v>
       </c>
@@ -7573,48 +7594,48 @@
       <c r="AC2" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="AD2" s="18" t="s">
+      <c r="AD2" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="AE2" s="17"/>
-      <c r="AF2" s="18" t="s">
+      <c r="AE2" s="13"/>
+      <c r="AF2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="AG2" s="17"/>
-      <c r="AH2" s="18" t="s">
+      <c r="AG2" s="13"/>
+      <c r="AH2" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="AI2" s="17"/>
-      <c r="AJ2" s="17"/>
-      <c r="AK2" s="18" t="s">
+      <c r="AI2" s="13"/>
+      <c r="AJ2" s="13"/>
+      <c r="AK2" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="AL2" s="17"/>
-      <c r="AM2" s="18" t="s">
+      <c r="AL2" s="13"/>
+      <c r="AM2" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="AN2" s="17"/>
+      <c r="AN2" s="13"/>
       <c r="AO2" s="5" t="s">
         <v>139</v>
       </c>
       <c r="AP2" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="AQ2" s="18" t="s">
+      <c r="AQ2" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="AR2" s="17"/>
+      <c r="AR2" s="13"/>
       <c r="AS2" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="AT2" s="17"/>
+      <c r="AT2" s="13"/>
       <c r="AU2" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
       <c r="C3" s="11" t="s">
         <v>143</v>
       </c>
@@ -7744,12 +7765,12 @@
       <c r="AS3" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="AT3" s="17"/>
+      <c r="AT3" s="13"/>
       <c r="AU3" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>157</v>
       </c>
@@ -7830,7 +7851,7 @@
       </c>
       <c r="AS4" s="9"/>
     </row>
-    <row r="5" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>165</v>
       </c>
@@ -7913,6 +7934,16 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:Q1"/>
+    <mergeCell ref="R1:Z1"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AT1:AT3"/>
     <mergeCell ref="AK1:AS1"/>
     <mergeCell ref="I2:K2"/>
@@ -7927,16 +7958,6 @@
     <mergeCell ref="AK2:AL2"/>
     <mergeCell ref="AM2:AN2"/>
     <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:Q1"/>
-    <mergeCell ref="R1:Z1"/>
-    <mergeCell ref="AA1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7945,125 +7966,125 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AU4"/>
-  <sheetFormatPr defaultColWidth="14.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="14.1796875" style="10"/>
+    <col min="1" max="16384" width="14.21875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="18" t="s">
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="12" t="s">
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="12" t="s">
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="12" t="s">
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17"/>
-      <c r="AK1" s="12" t="s">
+      <c r="AI1" s="13"/>
+      <c r="AJ1" s="13"/>
+      <c r="AK1" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17"/>
-      <c r="AQ1" s="17"/>
-      <c r="AR1" s="17"/>
-      <c r="AS1" s="17"/>
-      <c r="AT1" s="18" t="s">
+      <c r="AL1" s="13"/>
+      <c r="AM1" s="13"/>
+      <c r="AN1" s="13"/>
+      <c r="AO1" s="13"/>
+      <c r="AP1" s="13"/>
+      <c r="AQ1" s="13"/>
+      <c r="AR1" s="13"/>
+      <c r="AS1" s="13"/>
+      <c r="AT1" s="12" t="s">
         <v>129</v>
       </c>
       <c r="AU1" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18" t="s">
+    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="18" t="s">
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="18" t="s">
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="18" t="s">
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-      <c r="U2" s="18" t="s">
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="18" t="s">
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="Y2" s="17"/>
-      <c r="Z2" s="17"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
       <c r="AA2" s="5" t="s">
         <v>131</v>
       </c>
@@ -8073,48 +8094,48 @@
       <c r="AC2" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="AD2" s="18" t="s">
+      <c r="AD2" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="AE2" s="17"/>
-      <c r="AF2" s="18" t="s">
+      <c r="AE2" s="13"/>
+      <c r="AF2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="AG2" s="17"/>
-      <c r="AH2" s="18" t="s">
+      <c r="AG2" s="13"/>
+      <c r="AH2" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="AI2" s="17"/>
-      <c r="AJ2" s="17"/>
-      <c r="AK2" s="18" t="s">
+      <c r="AI2" s="13"/>
+      <c r="AJ2" s="13"/>
+      <c r="AK2" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="AL2" s="17"/>
-      <c r="AM2" s="18" t="s">
+      <c r="AL2" s="13"/>
+      <c r="AM2" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="AN2" s="17"/>
+      <c r="AN2" s="13"/>
       <c r="AO2" s="5" t="s">
         <v>139</v>
       </c>
       <c r="AP2" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="AQ2" s="18" t="s">
+      <c r="AQ2" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="AR2" s="17"/>
+      <c r="AR2" s="13"/>
       <c r="AS2" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="AT2" s="17"/>
+      <c r="AT2" s="13"/>
       <c r="AU2" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
       <c r="C3" s="11" t="s">
         <v>143</v>
       </c>
@@ -8244,12 +8265,12 @@
       <c r="AS3" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="AT3" s="17"/>
+      <c r="AT3" s="13"/>
       <c r="AU3" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>170</v>
       </c>
@@ -8332,6 +8353,16 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:Q1"/>
+    <mergeCell ref="R1:Z1"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AT1:AT3"/>
     <mergeCell ref="AK1:AS1"/>
     <mergeCell ref="I2:K2"/>
@@ -8346,16 +8377,6 @@
     <mergeCell ref="AK2:AL2"/>
     <mergeCell ref="AM2:AN2"/>
     <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:Q1"/>
-    <mergeCell ref="R1:Z1"/>
-    <mergeCell ref="AA1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8364,125 +8385,125 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AU10"/>
-  <sheetFormatPr defaultColWidth="14.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="14.1796875" style="10"/>
+    <col min="1" max="16384" width="14.21875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="18" t="s">
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="12" t="s">
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="12" t="s">
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="12" t="s">
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17"/>
-      <c r="AK1" s="12" t="s">
+      <c r="AI1" s="13"/>
+      <c r="AJ1" s="13"/>
+      <c r="AK1" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17"/>
-      <c r="AQ1" s="17"/>
-      <c r="AR1" s="17"/>
-      <c r="AS1" s="17"/>
-      <c r="AT1" s="18" t="s">
+      <c r="AL1" s="13"/>
+      <c r="AM1" s="13"/>
+      <c r="AN1" s="13"/>
+      <c r="AO1" s="13"/>
+      <c r="AP1" s="13"/>
+      <c r="AQ1" s="13"/>
+      <c r="AR1" s="13"/>
+      <c r="AS1" s="13"/>
+      <c r="AT1" s="12" t="s">
         <v>129</v>
       </c>
       <c r="AU1" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18" t="s">
+    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="18" t="s">
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="18" t="s">
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="18" t="s">
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-      <c r="U2" s="18" t="s">
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="18" t="s">
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="Y2" s="17"/>
-      <c r="Z2" s="17"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
       <c r="AA2" s="5" t="s">
         <v>131</v>
       </c>
@@ -8492,48 +8513,48 @@
       <c r="AC2" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="AD2" s="18" t="s">
+      <c r="AD2" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="AE2" s="17"/>
-      <c r="AF2" s="18" t="s">
+      <c r="AE2" s="13"/>
+      <c r="AF2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="AG2" s="17"/>
-      <c r="AH2" s="18" t="s">
+      <c r="AG2" s="13"/>
+      <c r="AH2" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="AI2" s="17"/>
-      <c r="AJ2" s="17"/>
-      <c r="AK2" s="18" t="s">
+      <c r="AI2" s="13"/>
+      <c r="AJ2" s="13"/>
+      <c r="AK2" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="AL2" s="17"/>
-      <c r="AM2" s="18" t="s">
+      <c r="AL2" s="13"/>
+      <c r="AM2" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="AN2" s="17"/>
+      <c r="AN2" s="13"/>
       <c r="AO2" s="5" t="s">
         <v>139</v>
       </c>
       <c r="AP2" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="AQ2" s="18" t="s">
+      <c r="AQ2" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="AR2" s="17"/>
+      <c r="AR2" s="13"/>
       <c r="AS2" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="AT2" s="17"/>
+      <c r="AT2" s="13"/>
       <c r="AU2" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
       <c r="C3" s="11" t="s">
         <v>143</v>
       </c>
@@ -8663,12 +8684,12 @@
       <c r="AS3" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="AT3" s="17"/>
+      <c r="AT3" s="13"/>
       <c r="AU3" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>172</v>
       </c>
@@ -8759,7 +8780,7 @@
       </c>
       <c r="AS4" s="9"/>
     </row>
-    <row r="5" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>181</v>
       </c>
@@ -8850,7 +8871,7 @@
       </c>
       <c r="AS5" s="9"/>
     </row>
-    <row r="6" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
         <v>183</v>
       </c>
@@ -8941,7 +8962,7 @@
       </c>
       <c r="AS6" s="9"/>
     </row>
-    <row r="7" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
         <v>185</v>
       </c>
@@ -9032,7 +9053,7 @@
       </c>
       <c r="AS7" s="9"/>
     </row>
-    <row r="8" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
         <v>188</v>
       </c>
@@ -9123,7 +9144,7 @@
       </c>
       <c r="AS8" s="9"/>
     </row>
-    <row r="9" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>189</v>
       </c>
@@ -9214,7 +9235,7 @@
       </c>
       <c r="AS9" s="9"/>
     </row>
-    <row r="10" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
         <v>190</v>
       </c>
@@ -9307,6 +9328,16 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:Q1"/>
+    <mergeCell ref="R1:Z1"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AT1:AT3"/>
     <mergeCell ref="AK1:AS1"/>
     <mergeCell ref="I2:K2"/>
@@ -9321,16 +9352,6 @@
     <mergeCell ref="AK2:AL2"/>
     <mergeCell ref="AM2:AN2"/>
     <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:Q1"/>
-    <mergeCell ref="R1:Z1"/>
-    <mergeCell ref="AA1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9339,125 +9360,125 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AU6"/>
-  <sheetFormatPr defaultColWidth="14.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="14.1796875" style="10"/>
+    <col min="1" max="16384" width="14.21875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="18" t="s">
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="12" t="s">
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="12" t="s">
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="12" t="s">
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17"/>
-      <c r="AK1" s="12" t="s">
+      <c r="AI1" s="13"/>
+      <c r="AJ1" s="13"/>
+      <c r="AK1" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17"/>
-      <c r="AQ1" s="17"/>
-      <c r="AR1" s="17"/>
-      <c r="AS1" s="17"/>
-      <c r="AT1" s="18" t="s">
+      <c r="AL1" s="13"/>
+      <c r="AM1" s="13"/>
+      <c r="AN1" s="13"/>
+      <c r="AO1" s="13"/>
+      <c r="AP1" s="13"/>
+      <c r="AQ1" s="13"/>
+      <c r="AR1" s="13"/>
+      <c r="AS1" s="13"/>
+      <c r="AT1" s="12" t="s">
         <v>129</v>
       </c>
       <c r="AU1" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18" t="s">
+    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="18" t="s">
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="18" t="s">
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="18" t="s">
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-      <c r="U2" s="18" t="s">
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="18" t="s">
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="Y2" s="17"/>
-      <c r="Z2" s="17"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
       <c r="AA2" s="5" t="s">
         <v>131</v>
       </c>
@@ -9467,48 +9488,48 @@
       <c r="AC2" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="AD2" s="18" t="s">
+      <c r="AD2" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="AE2" s="17"/>
-      <c r="AF2" s="18" t="s">
+      <c r="AE2" s="13"/>
+      <c r="AF2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="AG2" s="17"/>
-      <c r="AH2" s="18" t="s">
+      <c r="AG2" s="13"/>
+      <c r="AH2" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="AI2" s="17"/>
-      <c r="AJ2" s="17"/>
-      <c r="AK2" s="18" t="s">
+      <c r="AI2" s="13"/>
+      <c r="AJ2" s="13"/>
+      <c r="AK2" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="AL2" s="17"/>
-      <c r="AM2" s="18" t="s">
+      <c r="AL2" s="13"/>
+      <c r="AM2" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="AN2" s="17"/>
+      <c r="AN2" s="13"/>
       <c r="AO2" s="5" t="s">
         <v>139</v>
       </c>
       <c r="AP2" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="AQ2" s="18" t="s">
+      <c r="AQ2" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="AR2" s="17"/>
+      <c r="AR2" s="13"/>
       <c r="AS2" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="AT2" s="17"/>
+      <c r="AT2" s="13"/>
       <c r="AU2" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
       <c r="C3" s="11" t="s">
         <v>143</v>
       </c>
@@ -9638,12 +9659,12 @@
       <c r="AS3" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="AT3" s="17"/>
+      <c r="AT3" s="13"/>
       <c r="AU3" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>172</v>
       </c>
@@ -9744,7 +9765,7 @@
       </c>
       <c r="AS4" s="9"/>
     </row>
-    <row r="5" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>196</v>
       </c>
@@ -9837,7 +9858,7 @@
       </c>
       <c r="AS5" s="9"/>
     </row>
-    <row r="6" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
         <v>197</v>
       </c>
@@ -9932,6 +9953,16 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:Q1"/>
+    <mergeCell ref="R1:Z1"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AT1:AT3"/>
     <mergeCell ref="AK1:AS1"/>
     <mergeCell ref="I2:K2"/>
@@ -9946,16 +9977,6 @@
     <mergeCell ref="AK2:AL2"/>
     <mergeCell ref="AM2:AN2"/>
     <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:Q1"/>
-    <mergeCell ref="R1:Z1"/>
-    <mergeCell ref="AA1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9964,125 +9985,125 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AU4"/>
-  <sheetFormatPr defaultColWidth="14.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="14.1796875" style="10"/>
+    <col min="1" max="16384" width="14.21875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="18" t="s">
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="12" t="s">
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="12" t="s">
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="12" t="s">
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17"/>
-      <c r="AK1" s="12" t="s">
+      <c r="AI1" s="13"/>
+      <c r="AJ1" s="13"/>
+      <c r="AK1" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17"/>
-      <c r="AQ1" s="17"/>
-      <c r="AR1" s="17"/>
-      <c r="AS1" s="17"/>
-      <c r="AT1" s="18" t="s">
+      <c r="AL1" s="13"/>
+      <c r="AM1" s="13"/>
+      <c r="AN1" s="13"/>
+      <c r="AO1" s="13"/>
+      <c r="AP1" s="13"/>
+      <c r="AQ1" s="13"/>
+      <c r="AR1" s="13"/>
+      <c r="AS1" s="13"/>
+      <c r="AT1" s="12" t="s">
         <v>129</v>
       </c>
       <c r="AU1" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18" t="s">
+    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="18" t="s">
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="18" t="s">
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="18" t="s">
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-      <c r="U2" s="18" t="s">
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="18" t="s">
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="Y2" s="17"/>
-      <c r="Z2" s="17"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
       <c r="AA2" s="5" t="s">
         <v>131</v>
       </c>
@@ -10092,48 +10113,48 @@
       <c r="AC2" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="AD2" s="18" t="s">
+      <c r="AD2" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="AE2" s="17"/>
-      <c r="AF2" s="18" t="s">
+      <c r="AE2" s="13"/>
+      <c r="AF2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="AG2" s="17"/>
-      <c r="AH2" s="18" t="s">
+      <c r="AG2" s="13"/>
+      <c r="AH2" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="AI2" s="17"/>
-      <c r="AJ2" s="17"/>
-      <c r="AK2" s="18" t="s">
+      <c r="AI2" s="13"/>
+      <c r="AJ2" s="13"/>
+      <c r="AK2" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="AL2" s="17"/>
-      <c r="AM2" s="18" t="s">
+      <c r="AL2" s="13"/>
+      <c r="AM2" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="AN2" s="17"/>
+      <c r="AN2" s="13"/>
       <c r="AO2" s="5" t="s">
         <v>139</v>
       </c>
       <c r="AP2" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="AQ2" s="18" t="s">
+      <c r="AQ2" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="AR2" s="17"/>
+      <c r="AR2" s="13"/>
       <c r="AS2" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="AT2" s="17"/>
+      <c r="AT2" s="13"/>
       <c r="AU2" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
       <c r="C3" s="11" t="s">
         <v>143</v>
       </c>
@@ -10263,12 +10284,12 @@
       <c r="AS3" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="AT3" s="17"/>
+      <c r="AT3" s="13"/>
       <c r="AU3" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>199</v>
       </c>
@@ -10355,6 +10376,16 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:Q1"/>
+    <mergeCell ref="R1:Z1"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AT1:AT3"/>
     <mergeCell ref="AK1:AS1"/>
     <mergeCell ref="I2:K2"/>
@@ -10369,16 +10400,6 @@
     <mergeCell ref="AK2:AL2"/>
     <mergeCell ref="AM2:AN2"/>
     <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:Q1"/>
-    <mergeCell ref="R1:Z1"/>
-    <mergeCell ref="AA1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10387,125 +10408,125 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AU4"/>
-  <sheetFormatPr defaultColWidth="14.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="14.1796875" style="10"/>
+    <col min="1" max="16384" width="14.21875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="18" t="s">
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="12" t="s">
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="12" t="s">
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="12" t="s">
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17"/>
-      <c r="AK1" s="12" t="s">
+      <c r="AI1" s="13"/>
+      <c r="AJ1" s="13"/>
+      <c r="AK1" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17"/>
-      <c r="AQ1" s="17"/>
-      <c r="AR1" s="17"/>
-      <c r="AS1" s="17"/>
-      <c r="AT1" s="18" t="s">
+      <c r="AL1" s="13"/>
+      <c r="AM1" s="13"/>
+      <c r="AN1" s="13"/>
+      <c r="AO1" s="13"/>
+      <c r="AP1" s="13"/>
+      <c r="AQ1" s="13"/>
+      <c r="AR1" s="13"/>
+      <c r="AS1" s="13"/>
+      <c r="AT1" s="12" t="s">
         <v>129</v>
       </c>
       <c r="AU1" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18" t="s">
+    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="18" t="s">
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="18" t="s">
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="18" t="s">
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-      <c r="U2" s="18" t="s">
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="18" t="s">
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="Y2" s="17"/>
-      <c r="Z2" s="17"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
       <c r="AA2" s="5" t="s">
         <v>131</v>
       </c>
@@ -10515,48 +10536,48 @@
       <c r="AC2" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="AD2" s="18" t="s">
+      <c r="AD2" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="AE2" s="17"/>
-      <c r="AF2" s="18" t="s">
+      <c r="AE2" s="13"/>
+      <c r="AF2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="AG2" s="17"/>
-      <c r="AH2" s="18" t="s">
+      <c r="AG2" s="13"/>
+      <c r="AH2" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="AI2" s="17"/>
-      <c r="AJ2" s="17"/>
-      <c r="AK2" s="18" t="s">
+      <c r="AI2" s="13"/>
+      <c r="AJ2" s="13"/>
+      <c r="AK2" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="AL2" s="17"/>
-      <c r="AM2" s="18" t="s">
+      <c r="AL2" s="13"/>
+      <c r="AM2" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="AN2" s="17"/>
+      <c r="AN2" s="13"/>
       <c r="AO2" s="5" t="s">
         <v>139</v>
       </c>
       <c r="AP2" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="AQ2" s="18" t="s">
+      <c r="AQ2" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="AR2" s="17"/>
+      <c r="AR2" s="13"/>
       <c r="AS2" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="AT2" s="17"/>
+      <c r="AT2" s="13"/>
       <c r="AU2" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
       <c r="C3" s="11" t="s">
         <v>143</v>
       </c>
@@ -10686,12 +10707,12 @@
       <c r="AS3" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="AT3" s="17"/>
+      <c r="AT3" s="13"/>
       <c r="AU3" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>203</v>
       </c>
@@ -10774,6 +10795,16 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:Q1"/>
+    <mergeCell ref="R1:Z1"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AT1:AT3"/>
     <mergeCell ref="AK1:AS1"/>
     <mergeCell ref="I2:K2"/>
@@ -10788,16 +10819,6 @@
     <mergeCell ref="AK2:AL2"/>
     <mergeCell ref="AM2:AN2"/>
     <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:Q1"/>
-    <mergeCell ref="R1:Z1"/>
-    <mergeCell ref="AA1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10806,125 +10827,125 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AU4"/>
-  <sheetFormatPr defaultColWidth="14.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="14.1796875" style="10"/>
+    <col min="1" max="16384" width="14.21875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="18" t="s">
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="12" t="s">
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="12" t="s">
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="12" t="s">
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17"/>
-      <c r="AK1" s="12" t="s">
+      <c r="AI1" s="13"/>
+      <c r="AJ1" s="13"/>
+      <c r="AK1" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17"/>
-      <c r="AQ1" s="17"/>
-      <c r="AR1" s="17"/>
-      <c r="AS1" s="17"/>
-      <c r="AT1" s="18" t="s">
+      <c r="AL1" s="13"/>
+      <c r="AM1" s="13"/>
+      <c r="AN1" s="13"/>
+      <c r="AO1" s="13"/>
+      <c r="AP1" s="13"/>
+      <c r="AQ1" s="13"/>
+      <c r="AR1" s="13"/>
+      <c r="AS1" s="13"/>
+      <c r="AT1" s="12" t="s">
         <v>129</v>
       </c>
       <c r="AU1" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18" t="s">
+    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="18" t="s">
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="18" t="s">
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="18" t="s">
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-      <c r="U2" s="18" t="s">
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="18" t="s">
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="Y2" s="17"/>
-      <c r="Z2" s="17"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
       <c r="AA2" s="5" t="s">
         <v>131</v>
       </c>
@@ -10934,48 +10955,48 @@
       <c r="AC2" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="AD2" s="18" t="s">
+      <c r="AD2" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="AE2" s="17"/>
-      <c r="AF2" s="18" t="s">
+      <c r="AE2" s="13"/>
+      <c r="AF2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="AG2" s="17"/>
-      <c r="AH2" s="18" t="s">
+      <c r="AG2" s="13"/>
+      <c r="AH2" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="AI2" s="17"/>
-      <c r="AJ2" s="17"/>
-      <c r="AK2" s="18" t="s">
+      <c r="AI2" s="13"/>
+      <c r="AJ2" s="13"/>
+      <c r="AK2" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="AL2" s="17"/>
-      <c r="AM2" s="18" t="s">
+      <c r="AL2" s="13"/>
+      <c r="AM2" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="AN2" s="17"/>
+      <c r="AN2" s="13"/>
       <c r="AO2" s="5" t="s">
         <v>139</v>
       </c>
       <c r="AP2" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="AQ2" s="18" t="s">
+      <c r="AQ2" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="AR2" s="17"/>
+      <c r="AR2" s="13"/>
       <c r="AS2" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="AT2" s="17"/>
+      <c r="AT2" s="13"/>
       <c r="AU2" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
       <c r="C3" s="11" t="s">
         <v>143</v>
       </c>
@@ -11105,12 +11126,12 @@
       <c r="AS3" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="AT3" s="17"/>
+      <c r="AT3" s="13"/>
       <c r="AU3" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>203</v>
       </c>
@@ -11175,6 +11196,16 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:Q1"/>
+    <mergeCell ref="R1:Z1"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AT1:AT3"/>
     <mergeCell ref="AK1:AS1"/>
     <mergeCell ref="I2:K2"/>
@@ -11189,16 +11220,6 @@
     <mergeCell ref="AK2:AL2"/>
     <mergeCell ref="AM2:AN2"/>
     <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:Q1"/>
-    <mergeCell ref="R1:Z1"/>
-    <mergeCell ref="AA1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11207,125 +11228,125 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:AU4"/>
-  <sheetFormatPr defaultColWidth="14.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="14.1796875" style="10"/>
+    <col min="1" max="16384" width="14.21875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:47" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="18" t="s">
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="12" t="s">
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="12" t="s">
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="12" t="s">
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17"/>
-      <c r="AK1" s="12" t="s">
+      <c r="AI1" s="13"/>
+      <c r="AJ1" s="13"/>
+      <c r="AK1" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17"/>
-      <c r="AQ1" s="17"/>
-      <c r="AR1" s="17"/>
-      <c r="AS1" s="17"/>
-      <c r="AT1" s="18" t="s">
+      <c r="AL1" s="13"/>
+      <c r="AM1" s="13"/>
+      <c r="AN1" s="13"/>
+      <c r="AO1" s="13"/>
+      <c r="AP1" s="13"/>
+      <c r="AQ1" s="13"/>
+      <c r="AR1" s="13"/>
+      <c r="AS1" s="13"/>
+      <c r="AT1" s="12" t="s">
         <v>129</v>
       </c>
       <c r="AU1" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18" t="s">
+    <row r="2" spans="1:47" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="18" t="s">
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="18" t="s">
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="18" t="s">
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-      <c r="U2" s="18" t="s">
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="18" t="s">
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="Y2" s="17"/>
-      <c r="Z2" s="17"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
       <c r="AA2" s="5" t="s">
         <v>131</v>
       </c>
@@ -11335,48 +11356,48 @@
       <c r="AC2" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="AD2" s="18" t="s">
+      <c r="AD2" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="AE2" s="17"/>
-      <c r="AF2" s="18" t="s">
+      <c r="AE2" s="13"/>
+      <c r="AF2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="AG2" s="17"/>
-      <c r="AH2" s="18" t="s">
+      <c r="AG2" s="13"/>
+      <c r="AH2" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="AI2" s="17"/>
-      <c r="AJ2" s="17"/>
-      <c r="AK2" s="18" t="s">
+      <c r="AI2" s="13"/>
+      <c r="AJ2" s="13"/>
+      <c r="AK2" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="AL2" s="17"/>
-      <c r="AM2" s="18" t="s">
+      <c r="AL2" s="13"/>
+      <c r="AM2" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="AN2" s="17"/>
+      <c r="AN2" s="13"/>
       <c r="AO2" s="5" t="s">
         <v>139</v>
       </c>
       <c r="AP2" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="AQ2" s="18" t="s">
+      <c r="AQ2" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="AR2" s="17"/>
+      <c r="AR2" s="13"/>
       <c r="AS2" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="AT2" s="17"/>
+      <c r="AT2" s="13"/>
       <c r="AU2" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+    <row r="3" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
       <c r="C3" s="11" t="s">
         <v>143</v>
       </c>
@@ -11506,12 +11527,12 @@
       <c r="AS3" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="AT3" s="17"/>
+      <c r="AT3" s="13"/>
       <c r="AU3" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>208</v>
       </c>
@@ -11594,6 +11615,16 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:Q1"/>
+    <mergeCell ref="R1:Z1"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AT1:AT3"/>
     <mergeCell ref="AK1:AS1"/>
     <mergeCell ref="I2:K2"/>
@@ -11608,16 +11639,6 @@
     <mergeCell ref="AK2:AL2"/>
     <mergeCell ref="AM2:AN2"/>
     <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:Q1"/>
-    <mergeCell ref="R1:Z1"/>
-    <mergeCell ref="AA1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
